--- a/public/samples/organiser-projects-import.xlsx
+++ b/public/samples/organiser-projects-import.xlsx
@@ -421,7 +421,7 @@
         <v>Singapore</v>
       </c>
       <c r="C2" t="str">
-        <v>/samples/sample-submission.pdf</v>
+        <v>/samples/projects/proj-001.pdf</v>
       </c>
       <c r="D2" t="str">
         <v>https://www.youtube.com/watch?v=dQw4w9WgXcQ</v>
@@ -435,7 +435,7 @@
         <v>Malaysia</v>
       </c>
       <c r="C3" t="str">
-        <v>/samples/sample-submission.pdf</v>
+        <v>/samples/projects/proj-002.pdf</v>
       </c>
       <c r="D3" t="str">
         <v/>
